--- a/event_registration_forms/025_mental_health_workshop_attendance_form--event_registration_forms.xlsx
+++ b/event_registration_forms/025_mental_health_workshop_attendance_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_100,_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 100, 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_101,_'label':_'chatjimmy_2'}</t>
+          <t>chatjimmy_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 101, 'label': 'chatjimmy 2'}</t>
+          <t>chatjimmy 2</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_102,_'label':_'chatjimmy_3'}</t>
+          <t>chatjimmy_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 102, 'label': 'chatjimmy 3'}</t>
+          <t>chatjimmy 3</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_200,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 200, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_201,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 201, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_202,_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 202, 'label': 'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_300,_'label':_'present'}</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 300, 'label': 'present'}</t>
+          <t>present</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_301,_'label':_'absent'}</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 301, 'label': 'absent'}</t>
+          <t>absent</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_302,_'label':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 302, 'label': 'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
     </row>
